--- a/data/native-entity-ids_current.xlsx
+++ b/data/native-entity-ids_current.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BABD418-9F9A-41AE-A5A7-057426E3F29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA37308-F5D2-41C5-B93C-6B1826046830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32145" yWindow="3345" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31800" yWindow="3000" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="3" r:id="rId1"/>
@@ -22689,13 +22689,13 @@
         <f>HYPERLINK("#'native_geopairs'!A1", "native_geopairs")</f>
         <v>native_geopairs</v>
       </c>
+      <c r="B125" s="2" t="s">
+        <v>7100</v>
+      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>7025</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>7100</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
